--- a/artfynd/A 22006-2025 artfynd.xlsx
+++ b/artfynd/A 22006-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125469758</v>
+        <v>125469854</v>
       </c>
       <c r="B2" t="n">
-        <v>100279</v>
+        <v>58001</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,27 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>549716</v>
+        <v>549821</v>
       </c>
       <c r="R2" t="n">
-        <v>6411893</v>
+        <v>6411956</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -763,7 +767,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -782,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125469771</v>
+        <v>125469758</v>
       </c>
       <c r="B3" t="n">
-        <v>100279</v>
+        <v>100451</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,16 +818,8 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -834,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>549713</v>
+        <v>549716</v>
       </c>
       <c r="R3" t="n">
-        <v>6411866</v>
+        <v>6411893</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125469854</v>
+        <v>125469771</v>
       </c>
       <c r="B4" t="n">
-        <v>57883</v>
+        <v>100451</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,31 +908,35 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -945,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>549821</v>
+        <v>549713</v>
       </c>
       <c r="R4" t="n">
-        <v>6411956</v>
+        <v>6411866</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,6 +988,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 22006-2025 artfynd.xlsx
+++ b/artfynd/A 22006-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125469758</v>
+        <v>125469771</v>
       </c>
       <c r="B3" t="n">
         <v>100451</v>
@@ -818,8 +818,16 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -829,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>549716</v>
+        <v>549713</v>
       </c>
       <c r="R3" t="n">
-        <v>6411893</v>
+        <v>6411866</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,7 +900,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125469771</v>
+        <v>125469758</v>
       </c>
       <c r="B4" t="n">
         <v>100451</v>
@@ -925,16 +933,8 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -944,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>549713</v>
+        <v>549716</v>
       </c>
       <c r="R4" t="n">
-        <v>6411866</v>
+        <v>6411893</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 22006-2025 artfynd.xlsx
+++ b/artfynd/A 22006-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125469854</v>
+        <v>125469758</v>
       </c>
       <c r="B2" t="n">
-        <v>58001</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100506</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,31 +686,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>549821</v>
+        <v>549716</v>
       </c>
       <c r="R2" t="n">
-        <v>6411956</v>
+        <v>6411893</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -767,6 +758,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -788,12 +780,7 @@
         <v>125469771</v>
       </c>
       <c r="B3" t="n">
-        <v>100451</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100506</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,15 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125469758</v>
+        <v>125469854</v>
       </c>
       <c r="B4" t="n">
-        <v>100451</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58019</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -916,27 +898,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -944,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>549716</v>
+        <v>549821</v>
       </c>
       <c r="R4" t="n">
-        <v>6411893</v>
+        <v>6411956</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,7 +974,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 22006-2025 artfynd.xlsx
+++ b/artfynd/A 22006-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125469758</v>
       </c>
       <c r="B2" t="n">
-        <v>100506</v>
+        <v>100513</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>125469771</v>
       </c>
       <c r="B3" t="n">
-        <v>100506</v>
+        <v>100513</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22006-2025 artfynd.xlsx
+++ b/artfynd/A 22006-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125469758</v>
       </c>
       <c r="B2" t="n">
-        <v>100513</v>
+        <v>100516</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>125469771</v>
       </c>
       <c r="B3" t="n">
-        <v>100513</v>
+        <v>100516</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>125469854</v>
       </c>
       <c r="B4" t="n">
-        <v>58019</v>
+        <v>58020</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 22006-2025 artfynd.xlsx
+++ b/artfynd/A 22006-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125469758</v>
       </c>
       <c r="B2" t="n">
-        <v>100516</v>
+        <v>100520</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>125469771</v>
       </c>
       <c r="B3" t="n">
-        <v>100516</v>
+        <v>100520</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22006-2025 artfynd.xlsx
+++ b/artfynd/A 22006-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125469758</v>
       </c>
       <c r="B2" t="n">
-        <v>100520</v>
+        <v>100521</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>125469771</v>
       </c>
       <c r="B3" t="n">
-        <v>100520</v>
+        <v>100521</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22006-2025 artfynd.xlsx
+++ b/artfynd/A 22006-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125469758</v>
       </c>
       <c r="B2" t="n">
-        <v>100521</v>
+        <v>100523</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>125469771</v>
       </c>
       <c r="B3" t="n">
-        <v>100521</v>
+        <v>100523</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>125469854</v>
       </c>
       <c r="B4" t="n">
-        <v>58020</v>
+        <v>58021</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
